--- a/data/trans_bre/Q45B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 7,83</t>
+          <t>-0,74; 7,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,52</t>
+          <t>3,53; 10,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,71</t>
+          <t>-0,96; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 345,25</t>
+          <t>-18,56; 330,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>128,06; 2610,93</t>
+          <t>106,83; 2487,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 637,1</t>
+          <t>-49,64; 622,04</t>
         </is>
       </c>
     </row>
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,4</t>
+          <t>2,43; 7,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,07</t>
+          <t>0,02; 4,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,61</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,69; 832,4</t>
+          <t>80,63; 727,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 607,28</t>
+          <t>-6,42; 612,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,27 +794,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,16</t>
+          <t>4,96; 11,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,23</t>
+          <t>3,14; 9,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,92</t>
+          <t>3,86; 9,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>271,6; —</t>
+          <t>273,77; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>145,39; —</t>
+          <t>113,51; 2647,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,99</t>
+          <t>2,86; 9,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,62</t>
+          <t>1,96; 5,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,94</t>
+          <t>0,42; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,1; 976,69</t>
+          <t>68,93; 1301,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,75; —</t>
+          <t>-15,63; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,88</t>
+          <t>1,07; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,26</t>
+          <t>-1,28; 4,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,56</t>
+          <t>-2,28; 1,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1161,74</t>
+          <t>-0,68; 927,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,85; —</t>
+          <t>-78,94; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,25; 15,85</t>
+          <t>8,24; 15,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 8,06</t>
+          <t>1,03; 7,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,38</t>
+          <t>-1,96; 1,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,38; 829,94</t>
+          <t>13,95; 848,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,52</t>
+          <t>6,03; 10,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,24</t>
+          <t>4,41; 9,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,45</t>
+          <t>0,27; 3,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341,24; 4839,29</t>
+          <t>311,46; 3794,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>103,86; 605,76</t>
+          <t>112,95; 690,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,65; 764,54</t>
+          <t>9,21; 677,91</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,73</t>
+          <t>0,31; 4,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,95</t>
+          <t>3,01; 8,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,4</t>
+          <t>3,54; 7,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,75; 180,42</t>
+          <t>7,19; 186,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,51; 180,39</t>
+          <t>41,07; 178,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>141,34; 783,63</t>
+          <t>150,54; 747,05</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,87</t>
+          <t>4,74; 6,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,05</t>
+          <t>3,89; 5,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,26</t>
+          <t>1,91; 3,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196,86; 418,43</t>
+          <t>195,49; 412,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>127,3; 288,7</t>
+          <t>129,46; 283,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>150,8; 451,15</t>
+          <t>147,21; 454,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Q45B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/Q45B_R-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 7,48</t>
+          <t>-0,44; 8,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,44</t>
+          <t>3,34; 10,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,27</t>
+          <t>-0,9; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 330,04</t>
+          <t>-12,15; 373,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>106,83; 2487,78</t>
+          <t>130,46; 2867,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 622,04</t>
+          <t>-50,12; 656,2</t>
         </is>
       </c>
     </row>
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,27</t>
+          <t>2,42; 7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,06</t>
+          <t>0,25; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,62</t>
+          <t>0,19; 1,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,63; 727,92</t>
+          <t>75,91; 828,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 612,76</t>
+          <t>-6,41; 530,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,27 +794,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,38</t>
+          <t>5,04; 11,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,16</t>
+          <t>3,47; 9,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,06</t>
+          <t>3,81; 9,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273,77; —</t>
+          <t>272,33; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>113,51; 2647,66</t>
+          <t>142,79; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,06</t>
+          <t>2,61; 9,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,78</t>
+          <t>1,83; 5,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,91</t>
+          <t>0,38; 3,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,93; 1301,68</t>
+          <t>56,93; 1004,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,63; —</t>
+          <t>-41,59; —</t>
         </is>
       </c>
     </row>
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,14</t>
+          <t>1,18; 10,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,24</t>
+          <t>-0,82; 4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,93</t>
+          <t>-2,36; 1,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 927,96</t>
+          <t>-13,68; 1013,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-78,94; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,75</t>
+          <t>8,17; 16,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,89</t>
+          <t>0,95; 8,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,36</t>
+          <t>-2,26; 1,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,95; 848,38</t>
+          <t>7,76; 788,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,96</t>
+          <t>5,89; 10,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,52</t>
+          <t>4,2; 9,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,35</t>
+          <t>0,43; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311,46; 3794,69</t>
+          <t>310,57; 3624,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>112,95; 690,73</t>
+          <t>99,56; 718,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 677,91</t>
+          <t>-0,03; 643,5</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,81</t>
+          <t>0,53; 4,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,92</t>
+          <t>3,21; 8,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,52</t>
+          <t>3,5; 7,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,19; 186,33</t>
+          <t>9,19; 182,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,07; 178,99</t>
+          <t>39,35; 176,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>150,54; 747,05</t>
+          <t>138,27; 775,47</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,87</t>
+          <t>4,85; 6,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,93</t>
+          <t>3,9; 5,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,28</t>
+          <t>1,95; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>195,49; 412,09</t>
+          <t>198,07; 411,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>129,46; 283,93</t>
+          <t>132,9; 280,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>147,21; 454,57</t>
+          <t>166,69; 459,51</t>
         </is>
       </c>
     </row>
